--- a/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clovis est dans l'entrée. Papa sort le sac bleu. Papa, l'adulte, dit : on met la gourde. On met le chapeau. On met le doudou. Clovis écoute. Il met dans le sac ce que l'adulte a dit. La gourde est froide. Le chapeau est jaune. Le doudou sent le coton. Clovis ferme le sac. Parce qu'il a mis ce que papa a dit, le sac est prêt. Maman arrive. Elle dit : bravo. Ils sortent. Le sac est sur le dos de Clovis.</t>
+          <t>Clovis est dans l'entrée. Papa sort le sac bleu. Papa, l'adulte, dit : on met la gourde. On met le chapeau. On met le doudou. Clovis écoute. Il met dans le sac ce que l'adulte a dit. La gourde est froide. Le chapeau est jaune. Le doudou sent le coton. Clovis ferme le sac. Parce qu'il a mis ce que papa a dit, le sac est prêt. Maman arrive. Bravo. Ils sortent. Le sac est sur le dos de Clovis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Clovis est dans l'entrée. Papa sort le sac bleu. Papa, l'adulte, dit : on met la gourde. On met le chapeau. On met le doudou. Clovis écoute. Il met dans le sac ce que l'adulte a dit. La gourde est froide. Le chapeau est jaune. Le doudou sent le coton. Clovis ferme le sac. Parce qu'il a mis ce que papa a dit, le sac est prêt. Maman arrive.
+narrateur|Bravo. Ils sortent.
+narrateur|Le sac est sur le dos de Clovis.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa a parlé. Que met Clovis dans le sac ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Clovis a préparé le sac. Il a mis ce que l'adulte a dit. Papa et maman étaient là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Clovis enfile le sac. Papa ouvre la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Le sac est sur le dos de Clovis.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Papa a parlé. Que met Clovis dans le sac ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Clovis a préparé le sac. Il a mis ce que l'adulte a dit. Papa et maman étaient là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1849,7 @@
           <t>narrateur|Clovis enfile le sac. Papa ouvre la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clovis prépare son sac pour le parc</t>
+          <t>La fenêtre embuée</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La fenêtre est embuée. Nina voit le parc tout flou. Elle met la gourde, le chapeau et le doudou. Papa et maman disent bravo. Le sac est sur son dos.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clovis est dans l'entrée. Papa sort le sac bleu. Papa, l'adulte, dit : on met la gourde. On met le chapeau. On met le doudou. Clovis écoute. Il met dans le sac ce que l'adulte a dit. La gourde est froide. Le chapeau est jaune. Le doudou sent le coton. Clovis ferme le sac. Parce qu'il a mis ce que papa a dit, le sac est prêt. Maman arrive. Bravo. Ils sortent. Le sac est sur le dos de Clovis.</t>
+          <t>La fenêtre de l'entrée est toute embuée. On voit le parc au loin, tout flou. Un oiseau passe comme une ombre. Papa essuie un petit rond. Tu vois le bac à sable, Nina ? Oui. Il est tout pâle. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. On met dans le sac ce que l'adulte a dit. On met la gourde. On met le chapeau. On met le doudou. La gourde, le chapeau, le doudou. Nina écoute. Elle met dans le sac ce que l'adulte a dit. La gourde est froide. Tu la mets dans le sac ? Nina met la gourde. Bravo. La gourde est dedans. Le chapeau est jaune. Il est un peu souple. Voici le chapeau, Nina. Tu le mets dans le sac ? Nina met le chapeau. Bravo. Le chapeau est dedans. Le doudou sent le coton. Il est tout doux. Tu le mets dans le sac ? Nina met le doudou. Tu as mis ce que l'adulte a dit. Nina ferme le sac. Ça fait zzz. Le sac est prêt. Bravo. Tu as fait du bon travail. Le sac est prêt ? Oui, maman. Le petit rond sur la vitre reste clair.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,44 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Clovis est dans l'entrée. Papa sort le sac bleu. Papa, l'adulte, dit : on met la gourde. On met le chapeau. On met le doudou. Clovis écoute. Il met dans le sac ce que l'adulte a dit. La gourde est froide. Le chapeau est jaune. Le doudou sent le coton. Clovis ferme le sac. Parce qu'il a mis ce que papa a dit, le sac est prêt. Maman arrive.
-narrateur|Bravo. Ils sortent.
-narrateur|Le sac est sur le dos de Clovis.</t>
+          <t>narrateur|La fenêtre de l'entrée est toute embuée.
+narrateur|On voit le parc au loin, tout flou.
+narrateur|Un oiseau passe comme une ombre.
+narrateur|Papa essuie un petit rond.
+papa|Tu vois le bac à sable, Nina ?
+enfant-f|Oui. Il est tout pâle.
+narrateur|En ce moment, Nina cherche le sac.
+narrateur|Papa sort le sac bleu.
+narrateur|Le tissu sent le coton.
+papa|On met dans le sac ce que l'adulte a dit.
+papa|On met la gourde.
+papa|On met le chapeau.
+papa|On met le doudou.
+enfant-f|La gourde, le chapeau, le doudou.
+narrateur|Nina écoute.
+narrateur|Elle met dans le sac ce que l'adulte a dit.
+narrateur|La gourde est froide.
+papa|Tu la mets dans le sac ?
+narrateur|Nina met la gourde.
+papa|Bravo. La gourde est dedans.
+narrateur|Le chapeau est jaune.
+narrateur|Il est un peu souple.
+maman|Voici le chapeau, Nina.
+maman|Tu le mets dans le sac ?
+narrateur|Nina met le chapeau.
+maman|Bravo. Le chapeau est dedans.
+narrateur|Le doudou sent le coton.
+enfant-f|Il est tout doux.
+papa|Tu le mets dans le sac ?
+narrateur|Nina met le doudou.
+papa|Tu as mis ce que l'adulte a dit.
+narrateur|Nina ferme le sac.
+narrateur|Ça fait zzz.
+narrateur|Le sac est prêt.
+maman|Bravo. Tu as fait du bon travail.
+maman|Le sac est prêt ?
+enfant-f|Oui, maman.
+narrateur|Le petit rond sur la vitre reste clair.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,7 +1393,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa a parlé. Que met Clovis dans le sac ?</t>
+          <t>Papa a parlé. Que met Nina dans le sac ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,10 +1553,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa a parlé. Que met Clovis dans le sac ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Papa a parlé.
+narrateur|Que met Nina dans le sac ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Clovis a préparé le sac. Il a mis ce que l'adulte a dit. Papa et maman étaient là.</t>
+          <t>Nina a préparé le sac. Elle a mis ce que l'adulte a dit. La gourde, le chapeau, le doudou. Tu as fini de préparer le sac ? Oui, papa. Bravo. Le sac est prêt. On va au parc, maintenant ? Oui. Papa et maman sont là, près d'elle. Le parc n'est plus tout flou.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,10 +1725,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Clovis a préparé le sac. Il a mis ce que l'adulte a dit. Papa et maman étaient là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina a préparé le sac.
+narrateur|Elle a mis ce que l'adulte a dit.
+narrateur|La gourde, le chapeau, le doudou.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui, papa.
+papa|Bravo. Le sac est prêt.
+maman|On va au parc, maintenant ?
+enfant-f|Oui.
+narrateur|Papa et maman sont là, près d'elle.
+narrateur|Le parc n'est plus tout flou.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,7 +1761,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Clovis enfile le sac. Papa ouvre la porte.</t>
+          <t>Nina enfile le sac. Le sac est sur le dos de Nina. On ouvre la porte ? Papa ouvre la porte. Tu as ton sac, Nina ? Oui, maman. Bravo. Ils sortent. L'air sent l'herbe du parc.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,10 +1901,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Clovis enfile le sac. Papa ouvre la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina enfile le sac.
+narrateur|Le sac est sur le dos de Nina.
+papa|On ouvre la porte ?
+narrateur|Papa ouvre la porte.
+maman|Tu as ton sac, Nina ?
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|Ils sortent.
+narrateur|L'air sent l'herbe du parc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1874,7 +1936,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac bleu tape le dos de Nina. Le parc n'est plus derrière la vitre. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Bravo, Nina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,10 +2076,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le sac bleu tape le dos de Nina.
+narrateur|Le parc n'est plus derrière la vitre.
+enfant-f|Le sac est prêt.
+papa|Oui. Tu as mis ce que l'adulte a dit.
+maman|Bravo, Nina.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2036,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2140,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
@@ -1581,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a préparé le sac. Elle a mis ce que l'adulte a dit. La gourde, le chapeau, le doudou. Tu as fini de préparer le sac ? Oui, papa. Bravo. Le sac est prêt. On va au parc, maintenant ? Oui. Papa et maman sont là, près d'elle. Le parc n'est plus tout flou.</t>
+          <t>Nina a préparé le sac. Elle a mis ce que l'adulte a dit. La gourde, le chapeau, le doudou. Tu as fini de préparer le sac ? Oui, papa. Bravo. Le sac est prêt. On va au parc, maintenant ? Oui. Tu as la gourde, le chapeau, le doudou ? Oui. C'est dans le sac. On y va ensemble. Le parc n'est plus tout flou.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1733,7 +1733,9 @@
 papa|Bravo. Le sac est prêt.
 maman|On va au parc, maintenant ?
 enfant-f|Oui.
-narrateur|Papa et maman sont là, près d'elle.
+maman|Tu as la gourde, le chapeau, le doudou ?
+enfant-f|Oui. C'est dans le sac.
+papa|On y va ensemble.
 narrateur|Le parc n'est plus tout flou.</t>
         </is>
       </c>
@@ -2102,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2145,6 +2147,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La fenêtre embuée</t>
+          <t>Le bac à sable de Nina</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée de la maison</t>
+          <t>cuisine, entrée, parc</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clovis, papa, maman</t>
+          <t>Nina, papa, maman</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>215</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21">
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>La fenêtre est embuée. Nina voit le parc tout flou. Elle met la gourde, le chapeau et le doudou. Papa et maman disent bravo. Le sac est sur son dos.</t>
+          <t>Nina veut le bac à sable du parc. Papa dit gourde, chapeau, doudou. Elle pose une cuillère en bois. Elle la retire, met ce que l'adulte a dit. Le bac n'est plus flou.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La fenêtre de l'entrée est toute embuée. On voit le parc au loin, tout flou. Un oiseau passe comme une ombre. Papa essuie un petit rond. Tu vois le bac à sable, Nina ? Oui. Il est tout pâle. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. On met dans le sac ce que l'adulte a dit. On met la gourde. On met le chapeau. On met le doudou. La gourde, le chapeau, le doudou. Nina écoute. Elle met dans le sac ce que l'adulte a dit. La gourde est froide. Tu la mets dans le sac ? Nina met la gourde. Bravo. La gourde est dedans. Le chapeau est jaune. Il est un peu souple. Voici le chapeau, Nina. Tu le mets dans le sac ? Nina met le chapeau. Bravo. Le chapeau est dedans. Le doudou sent le coton. Il est tout doux. Tu le mets dans le sac ? Nina met le doudou. Tu as mis ce que l'adulte a dit. Nina ferme le sac. Ça fait zzz. Le sac est prêt. Bravo. Tu as fait du bon travail. Le sac est prêt ? Oui, maman. Le petit rond sur la vitre reste clair.</t>
+          <t>La bouilloire chante dans la cuisine. La vapeur fait un petit nuage. Papa essuie la table. Ça sent le thé. Une tasse fume encore. Maman plie le torchon. Le tiroir fait un petit clic. Près de la porte, la vitre est un peu floue. On voit le parc au loin. Un oiseau passe comme une ombre. Tu vois le bac à sable, Nina ? Oui. Je veux y aller. On y va. D'abord le sac. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. On met dans le sac ce que l'adulte a dit. La gourde, le chapeau, le doudou. La gourde, le chapeau, le doudou. Nina écoute. Elle voit une cuillère en bois. Elle la pose dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. On met ce que l'adulte a dit. Nina retire la cuillère. Elle met la gourde. La gourde est froide. Où est le chapeau ? Le chapeau jaune n'est pas là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clovis est dans l'entrée. Papa sort le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt; bleu. Papa, l'adulte, dit : on met la gourde. On met le chapeau. On met le doudou. Clovis écoute. Il met dans le sac ce que l'adulte a dit. La gourde est froide. Le chapeau est jaune. Le doudou sent le coton. Clovis ferme le sac. Parce qu'il a mis ce que papa a dit, le sac est prêt. Maman arrive. Elle dit : bravo. Ils sortent. Le sac est sur le dos de Clovis.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La bouilloire chante dans la cuisine. La vapeur fait un petit nuage. Papa essuie la table. Ça sent le thé. Une tasse fume encore. Maman plie le torchon. Le tiroir fait un petit clic. Près de la porte, la vitre est un peu floue. On voit le parc au loin. Un oiseau passe comme une ombre. Tu vois le bac à sable, Nina ? Oui. Je veux y aller. On y va. D'abord le sac. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. On met dans le sac ce que l'adulte a dit. La gourde, le chapeau, le doudou. La gourde, le chapeau, le doudou. Nina écoute. Elle voit une cuillère en bois. Elle la pose dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. On met ce que l'adulte a dit. Nina retire la cuillère. Elle met la gourde. La gourde est froide. Où est le chapeau ? Le chapeau jaune n'est pas là.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,44 +1324,36 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La fenêtre de l'entrée est toute embuée.
-narrateur|On voit le parc au loin, tout flou.
+          <t>narrateur|La bouilloire chante dans la cuisine.
+narrateur|La vapeur fait un petit nuage.
+narrateur|Papa essuie la table.
+narrateur|Ça sent le thé.
+narrateur|Une tasse fume encore.
+narrateur|Maman plie le torchon.
+narrateur|Le tiroir fait un petit clic.
+narrateur|Près de la porte, la vitre est un peu floue.
+narrateur|On voit le parc au loin.
 narrateur|Un oiseau passe comme une ombre.
-narrateur|Papa essuie un petit rond.
 papa|Tu vois le bac à sable, Nina ?
-enfant-f|Oui. Il est tout pâle.
+enfant-f|Oui. Je veux y aller.
+maman|On y va. D'abord le sac.
 narrateur|En ce moment, Nina cherche le sac.
 narrateur|Papa sort le sac bleu.
 narrateur|Le tissu sent le coton.
 papa|On met dans le sac ce que l'adulte a dit.
-papa|On met la gourde.
-papa|On met le chapeau.
-papa|On met le doudou.
+papa|La gourde, le chapeau, le doudou.
 enfant-f|La gourde, le chapeau, le doudou.
 narrateur|Nina écoute.
-narrateur|Elle met dans le sac ce que l'adulte a dit.
+narrateur|Elle voit une cuillère en bois.
+narrateur|Elle la pose dans le sac.
+narrateur|La cuillère fait un bruit dur.
+papa|La cuillère reste à la cuisine.
+papa|On met ce que l'adulte a dit.
+narrateur|Nina retire la cuillère.
+narrateur|Elle met la gourde.
 narrateur|La gourde est froide.
-papa|Tu la mets dans le sac ?
-narrateur|Nina met la gourde.
-papa|Bravo. La gourde est dedans.
-narrateur|Le chapeau est jaune.
-narrateur|Il est un peu souple.
-maman|Voici le chapeau, Nina.
-maman|Tu le mets dans le sac ?
-narrateur|Nina met le chapeau.
-maman|Bravo. Le chapeau est dedans.
-narrateur|Le doudou sent le coton.
-enfant-f|Il est tout doux.
-papa|Tu le mets dans le sac ?
-narrateur|Nina met le doudou.
-papa|Tu as mis ce que l'adulte a dit.
-narrateur|Nina ferme le sac.
-narrateur|Ça fait zzz.
-narrateur|Le sac est prêt.
-maman|Bravo. Tu as fait du bon travail.
-maman|Le sac est prêt ?
-enfant-f|Oui, maman.
-narrateur|Le petit rond sur la vitre reste clair.</t>
+enfant-f|Où est le chapeau ?
+narrateur|Le chapeau jaune n'est pas là.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1393,12 +1385,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa a parlé. Que met Nina dans le sac ?</t>
+          <t>Papa a parlé. Où Nina met-elle les affaires ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa a parlé. Que met Clovis dans le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a parlé. Où Nina met-elle les affaires ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le sac | mettre | gourde | chapeau | ce que papa a dit</t>
+          <t>le sac | dans le sac | elle met | mettre | gourde | chapeau | doudou | ce que papa a dit</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1428,7 +1420,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met dans le sac ce que l'adulte a dit. Que fait Clovis ?</t>
+          <t>Elle met les affaires dans le sac. Où les met-elle ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1477,7 +1469,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1554,7 +1546,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Papa a parlé.
-narrateur|Que met Nina dans le sac ?</t>
+narrateur|Où Nina met-elle les affaires ?</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1573,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a préparé le sac. Elle a mis ce que l'adulte a dit. La gourde, le chapeau, le doudou. Tu as fini de préparer le sac ? Oui, papa. Bravo. Le sac est prêt. On va au parc, maintenant ? Oui. Tu as la gourde, le chapeau, le doudou ? Oui. C'est dans le sac. On y va ensemble. Le parc n'est plus tout flou.</t>
+          <t>Voici le chapeau, Nina. Le chapeau est jaune. Il est un peu souple. Nina le met dans le sac. Le doudou sent le coton. Il est tout doux. Nina le met dans le sac. Tu as mis ce que l'adulte a dit. Nina ferme le sac. Ça fait zzz. Le sac est prêt. Le sac est prêt ? Oui, maman. Le petit nuage de la bouilloire s'en va. Tu as la gourde, le chapeau, le doudou ? Oui. C'est dans le sac. On peut sortir, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clovis a préparé le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Il a mis ce que l'adulte a dit. Papa et maman étaient là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Voici le chapeau, Nina. Le chapeau est jaune. Il est un peu souple. Nina le met dans le sac. Le doudou sent le coton. Il est tout doux. Nina le met dans le sac. Tu as mis ce que l'adulte a dit. Nina ferme le sac. Ça fait zzz. Le sac est prêt. Le sac est prêt ? Oui, maman. Le petit nuage de la bouilloire s'en va. Tu as la gourde, le chapeau, le doudou ? Oui. C'est dans le sac. On peut sortir, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1725,18 +1717,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina a préparé le sac.
-narrateur|Elle a mis ce que l'adulte a dit.
-narrateur|La gourde, le chapeau, le doudou.
-papa|Tu as fini de préparer le sac ?
-enfant-f|Oui, papa.
-papa|Bravo. Le sac est prêt.
-maman|On va au parc, maintenant ?
-enfant-f|Oui.
+          <t>maman|Voici le chapeau, Nina.
+narrateur|Le chapeau est jaune.
+narrateur|Il est un peu souple.
+narrateur|Nina le met dans le sac.
+narrateur|Le doudou sent le coton.
+enfant-f|Il est tout doux.
+narrateur|Nina le met dans le sac.
+papa|Tu as mis ce que l'adulte a dit.
+narrateur|Nina ferme le sac.
+narrateur|Ça fait zzz.
+narrateur|Le sac est prêt.
+maman|Le sac est prêt ?
+enfant-f|Oui, maman.
+narrateur|Le petit nuage de la bouilloire s'en va.
 maman|Tu as la gourde, le chapeau, le doudou ?
 enfant-f|Oui. C'est dans le sac.
-papa|On y va ensemble.
-narrateur|Le parc n'est plus tout flou.</t>
+papa|On peut sortir, maintenant.</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1760,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina enfile le sac. Le sac est sur le dos de Nina. On ouvre la porte ? Papa ouvre la porte. Tu as ton sac, Nina ? Oui, maman. Bravo. Ils sortent. L'air sent l'herbe du parc.</t>
+          <t>Nina enfile le sac. Le sac est sur le dos de Nina. On ouvre la porte. Papa ouvre la porte. Tu as ton sac, Nina ? Oui, maman. Ils sortent. L'air sent l'herbe du parc. Le bac à sable n'est plus flou. Il est vrai, maintenant. Oui. On y va ensemble. Le sable est un peu pâle. Nina s'accroupit. Elle touche le sable. Il est un peu frais. Il coule, maman. Oui. Tu peux en prendre un peu. Nina ferme la main. Le sable reste un moment.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clovis enfile le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Papa ouvre la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina enfile le sac. Le sac est sur le dos de Nina. On ouvre la porte. Papa ouvre la porte. Tu as ton sac, Nina ? Oui, maman. Ils sortent. L'air sent l'herbe du parc. Le bac à sable n'est plus flou. Il est vrai, maintenant. Oui. On y va ensemble. Le sable est un peu pâle. Nina s'accroupit. Elle touche le sable. Il est un peu frais. Il coule, maman. Oui. Tu peux en prendre un peu. Nina ferme la main. Le sable reste un moment.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1905,13 +1902,23 @@
         <is>
           <t>narrateur|Nina enfile le sac.
 narrateur|Le sac est sur le dos de Nina.
-papa|On ouvre la porte ?
+papa|On ouvre la porte.
 narrateur|Papa ouvre la porte.
 maman|Tu as ton sac, Nina ?
 enfant-f|Oui, maman.
-maman|Bravo.
 narrateur|Ils sortent.
-narrateur|L'air sent l'herbe du parc.</t>
+narrateur|L'air sent l'herbe du parc.
+narrateur|Le bac à sable n'est plus flou.
+enfant-f|Il est vrai, maintenant.
+papa|Oui. On y va ensemble.
+narrateur|Le sable est un peu pâle.
+narrateur|Nina s'accroupit.
+narrateur|Elle touche le sable.
+narrateur|Il est un peu frais.
+enfant-f|Il coule, maman.
+maman|Oui. Tu peux en prendre un peu.
+narrateur|Nina ferme la main.
+narrateur|Le sable reste un moment.</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le sac bleu tape le dos de Nina. Le parc n'est plus derrière la vitre. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Bravo, Nina. L'histoire est finie.</t>
+          <t>Le sac bleu tape le dos de Nina. Le parc n'est plus derrière la vitre. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Le bac à sable t'attend. Nina ouvre encore la main. Le sable retombe, tout fin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sac bleu tape le dos de Nina. Le parc n'est plus derrière la vitre. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Le bac à sable t'attend. Nina ouvre encore la main. Le sable retombe, tout fin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2006,7 +2013,7 @@
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2082,7 +2089,9 @@
 narrateur|Le parc n'est plus derrière la vitre.
 enfant-f|Le sac est prêt.
 papa|Oui. Tu as mis ce que l'adulte a dit.
-maman|Bravo, Nina.
+maman|Le bac à sable t'attend.
+narrateur|Nina ouvre encore la main.
+narrateur|Le sable retombe, tout fin.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2104,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2186,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le bac à sable de Nina</t>
+          <t>La pomme du marché</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nina veut le bac à sable du parc. Papa dit gourde, chapeau, doudou. Elle pose une cuillère en bois. Elle la retire, met ce que l'adulte a dit. Le bac n'est plus flou.</t>
+          <t>Nina veut une pomme brillante au hall. Elle pose une cuillère, la retire, trouve le chapeau. La pomme est froide dans sa main.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La bouilloire chante dans la cuisine. La vapeur fait un petit nuage. Papa essuie la table. Ça sent le thé. Une tasse fume encore. Maman plie le torchon. Le tiroir fait un petit clic. Près de la porte, la vitre est un peu floue. On voit le parc au loin. Un oiseau passe comme une ombre. Tu vois le bac à sable, Nina ? Oui. Je veux y aller. On y va. D'abord le sac. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. On met dans le sac ce que l'adulte a dit. La gourde, le chapeau, le doudou. La gourde, le chapeau, le doudou. Nina écoute. Elle voit une cuillère en bois. Elle la pose dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. On met ce que l'adulte a dit. Nina retire la cuillère. Elle met la gourde. La gourde est froide. Où est le chapeau ? Le chapeau jaune n'est pas là.</t>
+          <t>Les caisses du hall râpent le pavé. Même d'ici, ça sent les pommes. La bouilloire chante dans la cuisine. La vapeur fait un petit nuage. Papa essuie la table. Ça sent le thé. Une tasse fume encore. Maman plie le torchon. Le tiroir fait un petit clic. Près de la porte, la vitre est un peu floue. Tu vois le hall, Nina ? Oui. Je veux une pomme qui brille. On y va, avec le sac. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. Prends de l'eau, le hall est long. Nina met la gourde. La gourde est froide. Elle voit une cuillère en bois. Elle la pose dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. Le hall n'en a pas besoin. Nina retire la cuillère. Où est le chapeau ? Le chapeau jaune n'est pas là. Sous la chaise, peut-être. Nina se penche. Le chapeau est souple, un peu poussiéreux. Elle le secoue, tout doux. Elle le met dans le sac. Ton doudou voudra la pomme aussi. Le doudou sent le coton. Il est tout doux. Nina le met dans le sac. Tu fermes ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La bouilloire chante dans la cuisine. La vapeur fait un petit nuage. Papa essuie la table. Ça sent le thé. Une tasse fume encore. Maman plie le torchon. Le tiroir fait un petit clic. Près de la porte, la vitre est un peu floue. On voit le parc au loin. Un oiseau passe comme une ombre. Tu vois le bac à sable, Nina ? Oui. Je veux y aller. On y va. D'abord le sac. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. On met dans le sac ce que l'adulte a dit. La gourde, le chapeau, le doudou. La gourde, le chapeau, le doudou. Nina écoute. Elle voit une cuillère en bois. Elle la pose dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. On met ce que l'adulte a dit. Nina retire la cuillère. Elle met la gourde. La gourde est froide. Où est le chapeau ? Le chapeau jaune n'est pas là.</t>
+          <t>Les caisses du hall râpent le pavé. Même d'ici, ça sent les pommes. La bouilloire chante dans la cuisine. La vapeur fait un petit nuage. Papa essuie la table. Ça sent le thé. Une tasse fume encore. Maman plie le torchon. Le tiroir fait un petit clic. Près de la porte, la vitre est un peu floue. Tu vois le hall, Nina ? Oui. Je veux une pomme qui brille. On y va, avec le sac. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. Prends de l'eau, le hall est long. Nina met la gourde. La gourde est froide. Elle voit une cuillère en bois. Elle la pose dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. Le hall n'en a pas besoin. Nina retire la cuillère. Où est le chapeau ? Le chapeau jaune n'est pas là. Sous la chaise, peut-être. Nina se penche. Le chapeau est souple, un peu poussiéreux. Elle le secoue, tout doux. Elle le met dans le sac. Ton doudou voudra la pomme aussi. Le doudou sent le coton. Il est tout doux. Nina le met dans le sac. Tu fermes ?</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,7 +1324,9 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La bouilloire chante dans la cuisine.
+          <t>narrateur|Les caisses du hall râpent le pavé.
+narrateur|Même d'ici, ça sent les pommes.
+narrateur|La bouilloire chante dans la cuisine.
 narrateur|La vapeur fait un petit nuage.
 narrateur|Papa essuie la table.
 narrateur|Ça sent le thé.
@@ -1332,28 +1334,34 @@
 narrateur|Maman plie le torchon.
 narrateur|Le tiroir fait un petit clic.
 narrateur|Près de la porte, la vitre est un peu floue.
-narrateur|On voit le parc au loin.
-narrateur|Un oiseau passe comme une ombre.
-papa|Tu vois le bac à sable, Nina ?
-enfant-f|Oui. Je veux y aller.
-maman|On y va. D'abord le sac.
+papa|Tu vois le hall, Nina ?
+enfant-f|Oui.
+enfant-f|Je veux une pomme qui brille.
+maman|On y va, avec le sac.
 narrateur|En ce moment, Nina cherche le sac.
 narrateur|Papa sort le sac bleu.
 narrateur|Le tissu sent le coton.
-papa|On met dans le sac ce que l'adulte a dit.
-papa|La gourde, le chapeau, le doudou.
-enfant-f|La gourde, le chapeau, le doudou.
-narrateur|Nina écoute.
+papa|Prends de l'eau, le hall est long.
+narrateur|Nina met la gourde.
+narrateur|La gourde est froide.
 narrateur|Elle voit une cuillère en bois.
 narrateur|Elle la pose dans le sac.
 narrateur|La cuillère fait un bruit dur.
 papa|La cuillère reste à la cuisine.
-papa|On met ce que l'adulte a dit.
+maman|Le hall n'en a pas besoin.
 narrateur|Nina retire la cuillère.
-narrateur|Elle met la gourde.
-narrateur|La gourde est froide.
 enfant-f|Où est le chapeau ?
-narrateur|Le chapeau jaune n'est pas là.</t>
+narrateur|Le chapeau jaune n'est pas là.
+maman|Sous la chaise, peut-être.
+narrateur|Nina se penche.
+narrateur|Le chapeau est souple, un peu poussiéreux.
+narrateur|Elle le secoue, tout doux.
+narrateur|Elle le met dans le sac.
+papa|Ton doudou voudra la pomme aussi.
+narrateur|Le doudou sent le coton.
+enfant-f|Il est tout doux.
+narrateur|Nina le met dans le sac.
+maman|Tu fermes ?</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1385,12 +1393,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa a parlé. Où Nina met-elle les affaires ?</t>
+          <t>Nina prépare le sac. Où met-elle les affaires ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Papa a parlé. Où Nina met-elle les affaires ?</t>
+          <t>Nina prépare le sac. Où met-elle les affaires ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1405,7 +1413,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le sac | dans le sac | elle met | mettre | gourde | chapeau | doudou | ce que papa a dit</t>
+          <t>le sac | dans le sac | il met | elle met | mettre</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1420,7 +1428,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle met les affaires dans le sac. Où les met-elle ?</t>
+          <t>Elle met les affaires dans le sac. Où les met Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1545,8 +1553,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa a parlé.
-narrateur|Où Nina met-elle les affaires ?</t>
+          <t>narrateur|Nina prépare le sac.
+narrateur|Où met-elle les affaires ?</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1581,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Voici le chapeau, Nina. Le chapeau est jaune. Il est un peu souple. Nina le met dans le sac. Le doudou sent le coton. Il est tout doux. Nina le met dans le sac. Tu as mis ce que l'adulte a dit. Nina ferme le sac. Ça fait zzz. Le sac est prêt. Le sac est prêt ? Oui, maman. Le petit nuage de la bouilloire s'en va. Tu as la gourde, le chapeau, le doudou ? Oui. C'est dans le sac. On peut sortir, maintenant.</t>
+          <t>Nina ferme le sac. Ça fait zzz. Le sac bleu est prêt. Le sac est prêt ? Oui, maman. Merci, Nina. Tu as laissé la cuillère ici. Le petit nuage de la bouilloire s'en va. On peut sortir, maintenant. La pomme m'attend. Oui, elle brille déjà, là-bas. Nina enfile le sac. Le sac est sur le dos de Nina. Tu as ton sac, Nina ? Oui, maman. On ouvre la porte. Papa ouvre la porte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Voici le chapeau, Nina. Le chapeau est jaune. Il est un peu souple. Nina le met dans le sac. Le doudou sent le coton. Il est tout doux. Nina le met dans le sac. Tu as mis ce que l'adulte a dit. Nina ferme le sac. Ça fait zzz. Le sac est prêt. Le sac est prêt ? Oui, maman. Le petit nuage de la bouilloire s'en va. Tu as la gourde, le chapeau, le doudou ? Oui. C'est dans le sac. On peut sortir, maintenant.</t>
+          <t>Nina ferme le sac. Ça fait zzz. Le sac bleu est prêt. Le sac est prêt ? Oui, maman. Merci, Nina. Tu as laissé la cuillère ici. Le petit nuage de la bouilloire s'en va. On peut sortir, maintenant. La pomme m'attend. Oui, elle brille déjà, là-bas. Nina enfile le sac. Le sac est sur le dos de Nina. Tu as ton sac, Nina ? Oui, maman. On ouvre la porte. Papa ouvre la porte.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1641,7 +1649,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1717,23 +1725,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>maman|Voici le chapeau, Nina.
-narrateur|Le chapeau est jaune.
-narrateur|Il est un peu souple.
-narrateur|Nina le met dans le sac.
-narrateur|Le doudou sent le coton.
-enfant-f|Il est tout doux.
-narrateur|Nina le met dans le sac.
-papa|Tu as mis ce que l'adulte a dit.
-narrateur|Nina ferme le sac.
+          <t>narrateur|Nina ferme le sac.
 narrateur|Ça fait zzz.
-narrateur|Le sac est prêt.
+narrateur|Le sac bleu est prêt.
 maman|Le sac est prêt ?
 enfant-f|Oui, maman.
+papa|Merci, Nina.
+papa|Tu as laissé la cuillère ici.
 narrateur|Le petit nuage de la bouilloire s'en va.
-maman|Tu as la gourde, le chapeau, le doudou ?
-enfant-f|Oui. C'est dans le sac.
-papa|On peut sortir, maintenant.</t>
+maman|On peut sortir, maintenant.
+enfant-f|La pomme m'attend.
+papa|Oui, elle brille déjà, là-bas.
+narrateur|Nina enfile le sac.
+narrateur|Le sac est sur le dos de Nina.
+maman|Tu as ton sac, Nina ?
+enfant-f|Oui, maman.
+papa|On ouvre la porte.
+narrateur|Papa ouvre la porte.</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina enfile le sac. Le sac est sur le dos de Nina. On ouvre la porte. Papa ouvre la porte. Tu as ton sac, Nina ? Oui, maman. Ils sortent. L'air sent l'herbe du parc. Le bac à sable n'est plus flou. Il est vrai, maintenant. Oui. On y va ensemble. Le sable est un peu pâle. Nina s'accroupit. Elle touche le sable. Il est un peu frais. Il coule, maman. Oui. Tu peux en prendre un peu. Nina ferme la main. Le sable reste un moment.</t>
+          <t>Ils sortent. L'air sent les caisses et le fruit. Le hall n'est plus flou. Il est vrai, maintenant. Oui, on y va ensemble. Une pomme rouge brille sur une caisse. Nina s'accroupit. Elle touche la peau lisse. Elle est un peu froide, un peu sucrée. Elle brille, maman. Tu la choisis ? Celle-là. Nina ferme la main autour de la pomme. Le fruit reste un moment, tout rond. On la sent ensemble ? Oui. Nina approche la pomme de son nez. Ça sent le sucre et la peau. Tu l'as trouvée. Une caisse râpe encore le pavé, tout loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nina enfile le sac. Le sac est sur le dos de Nina. On ouvre la porte. Papa ouvre la porte. Tu as ton sac, Nina ? Oui, maman. Ils sortent. L'air sent l'herbe du parc. Le bac à sable n'est plus flou. Il est vrai, maintenant. Oui. On y va ensemble. Le sable est un peu pâle. Nina s'accroupit. Elle touche le sable. Il est un peu frais. Il coule, maman. Oui. Tu peux en prendre un peu. Nina ferme la main. Le sable reste un moment.</t>
+          <t>Ils sortent. L'air sent les caisses et le fruit. Le hall n'est plus flou. Il est vrai, maintenant. Oui, on y va ensemble. Une pomme rouge brille sur une caisse. Nina s'accroupit. Elle touche la peau lisse. Elle est un peu froide, un peu sucrée. Elle brille, maman. Tu la choisis ? Celle-là. Nina ferme la main autour de la pomme. Le fruit reste un moment, tout rond. On la sent ensemble ? Oui. Nina approche la pomme de son nez. Ça sent le sucre et la peau. Tu l'as trouvée. Une caisse râpe encore le pavé, tout loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1828,7 +1836,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1900,25 +1908,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nina enfile le sac.
-narrateur|Le sac est sur le dos de Nina.
-papa|On ouvre la porte.
-narrateur|Papa ouvre la porte.
-maman|Tu as ton sac, Nina ?
-enfant-f|Oui, maman.
-narrateur|Ils sortent.
-narrateur|L'air sent l'herbe du parc.
-narrateur|Le bac à sable n'est plus flou.
+          <t>narrateur|Ils sortent.
+narrateur|L'air sent les caisses et le fruit.
+narrateur|Le hall n'est plus flou.
 enfant-f|Il est vrai, maintenant.
-papa|Oui. On y va ensemble.
-narrateur|Le sable est un peu pâle.
+papa|Oui, on y va ensemble.
+narrateur|Une pomme rouge brille sur une caisse.
 narrateur|Nina s'accroupit.
-narrateur|Elle touche le sable.
-narrateur|Il est un peu frais.
-enfant-f|Il coule, maman.
-maman|Oui. Tu peux en prendre un peu.
-narrateur|Nina ferme la main.
-narrateur|Le sable reste un moment.</t>
+narrateur|Elle touche la peau lisse.
+narrateur|Elle est un peu froide, un peu sucrée.
+enfant-f|Elle brille, maman.
+maman|Tu la choisis ?
+enfant-f|Celle-là.
+narrateur|Nina ferme la main autour de la pomme.
+narrateur|Le fruit reste un moment, tout rond.
+papa|On la sent ensemble ?
+enfant-f|Oui.
+narrateur|Nina approche la pomme de son nez.
+narrateur|Ça sent le sucre et la peau.
+maman|Tu l'as trouvée.
+narrateur|Une caisse râpe encore le pavé, tout loin.</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le sac bleu tape le dos de Nina. Le parc n'est plus derrière la vitre. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Le bac à sable t'attend. Nina ouvre encore la main. Le sable retombe, tout fin. L'histoire est finie.</t>
+          <t>Nina ouvre encore la main. La pomme rouge brille dans sa paume. Elle est à moi. Oui, tu es arrivée au hall. Le sac bleu tape le dos de Nina. Le thé de la cuisine est loin, maintenant. Bravo, tu as préparé la sortie. La peau lisse reste froide contre sa main.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le sac bleu tape le dos de Nina. Le parc n'est plus derrière la vitre. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Le bac à sable t'attend. Nina ouvre encore la main. Le sable retombe, tout fin. L'histoire est finie.</t>
+          <t>Nina ouvre encore la main. La pomme rouge brille dans sa paume. Elle est à moi. Oui, tu es arrivée au hall. Le sac bleu tape le dos de Nina. Le thé de la cuisine est loin, maintenant. Bravo, tu as préparé la sortie. La peau lisse reste froide contre sa main.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2006,14 +2015,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2085,14 +2094,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le sac bleu tape le dos de Nina.
-narrateur|Le parc n'est plus derrière la vitre.
-enfant-f|Le sac est prêt.
-papa|Oui. Tu as mis ce que l'adulte a dit.
-maman|Le bac à sable t'attend.
-narrateur|Nina ouvre encore la main.
-narrateur|Le sable retombe, tout fin.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina ouvre encore la main.
+narrateur|La pomme rouge brille dans sa paume.
+enfant-f|Elle est à moi.
+papa|Oui, tu es arrivée au hall.
+narrateur|Le sac bleu tape le dos de Nina.
+narrateur|Le thé de la cuisine est loin, maintenant.
+maman|Bravo, tu as préparé la sortie.
+narrateur|La peau lisse reste froide contre sa main.</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2191,6 +2200,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine, entrée, parc</t>
+          <t>cuisine puis hall du marché</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
@@ -1954,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nina ouvre encore la main. La pomme rouge brille dans sa paume. Elle est à moi. Oui, tu es arrivée au hall. Le sac bleu tape le dos de Nina. Le thé de la cuisine est loin, maintenant. Bravo, tu as préparé la sortie. La peau lisse reste froide contre sa main.</t>
+          <t>Nina ouvre encore la main. La pomme rouge brille dans sa paume. Elle est à moi. Oui, tu es arrivée au hall. Le sac bleu tape le dos de Nina. Le thé de la cuisine est loin, maintenant. Merci pour le sac, Nina. La peau lisse reste froide contre sa main.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Nina ouvre encore la main. La pomme rouge brille dans sa paume. Elle est à moi. Oui, tu es arrivée au hall. Le sac bleu tape le dos de Nina. Le thé de la cuisine est loin, maintenant. Bravo, tu as préparé la sortie. La peau lisse reste froide contre sa main.</t>
+          <t>Nina ouvre encore la main. La pomme rouge brille dans sa paume. Elle est à moi. Oui, tu es arrivée au hall. Le sac bleu tape le dos de Nina. Le thé de la cuisine est loin, maintenant. Merci pour le sac, Nina. La peau lisse reste froide contre sa main.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
 papa|Oui, tu es arrivée au hall.
 narrateur|Le sac bleu tape le dos de Nina.
 narrateur|Le thé de la cuisine est loin, maintenant.
-maman|Bravo, tu as préparé la sortie.
+maman|Merci pour le sac, Nina.
 narrateur|La peau lisse reste froide contre sa main.</t>
         </is>
       </c>
@@ -2122,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2207,6 +2207,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-06.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nina veut une pomme brillante au hall. Elle pose une cuillère, la retire, trouve le chapeau. La pomme est froide dans sa main.</t>
+          <t>Derrière la vitre floue, les caisses râpent le pavé. Un éclat de caisse cligne sur le verre. Nina veut une pomme du hall, maintenant, dans son sac. Elle jette tout d'un coup : la cuillère, le zip qui mord. Elle refuse de forcer, range, trouve le chapeau. Au hall, la pomme roule. Elle refuse de foncer, retrouve l'éclat. La pomme paie le début.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les caisses du hall râpent le pavé. Même d'ici, ça sent les pommes. La bouilloire chante dans la cuisine. La vapeur fait un petit nuage. Papa essuie la table. Ça sent le thé. Une tasse fume encore. Maman plie le torchon. Le tiroir fait un petit clic. Près de la porte, la vitre est un peu floue. Tu vois le hall, Nina ? Oui. Je veux une pomme qui brille. On y va, avec le sac. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. Prends de l'eau, le hall est long. Nina met la gourde. La gourde est froide. Elle voit une cuillère en bois. Elle la pose dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. Le hall n'en a pas besoin. Nina retire la cuillère. Où est le chapeau ? Le chapeau jaune n'est pas là. Sous la chaise, peut-être. Nina se penche. Le chapeau est souple, un peu poussiéreux. Elle le secoue, tout doux. Elle le met dans le sac. Ton doudou voudra la pomme aussi. Le doudou sent le coton. Il est tout doux. Nina le met dans le sac. Tu fermes ?</t>
+          <t>Derrière la vitre floue, les caisses râpent le pavé. Même ici, ça sent la pomme du hall. Nina connaît cette cuisine, ses recoins. La bouilloire chante, petite. Un nuage de vapeur touche la vitre. Sur le verre, un éclat de caisse cligne. Il vient du hall, si près. Nina ne sait pas à quoi il servira. Papa essuie la table. La nappe sent le thé chaud. Une tasse fume près du torchon. Maman plie le torchon, sans se presser. Le tiroir fait un petit clic. Nina, tu sens la pomme ? Oui, papa. Je veux une pomme, maintenant ! On y va, avec le sac. En ce moment, Nina saisit le sac bleu. Le tissu sent le coton, un peu rêche. Prends de l'eau, le hall est long. Nina prend la gourde froide. Le bouchon est lisse sous le doigt. Je mets tout, d'un coup ! Elle pousse la gourde, trop vite. Une cuillère en bois attend près du bol. Nina la jette dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. Le hall n'en a pas besoin. Nina veut fermer, sans attendre. Où est mon chapeau ? Le chapeau jaune n'est pas là. Nina bourre le sac, quand même. Le zip mord la sangle. Ça reste coincé ! Elle tire plus fort. Le zip refuse. Le sourire de Nina disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Papa se baisse à sa hauteur. Tu regardes le sac ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Les caisses du hall râpent le pavé. Même d'ici, ça sent les pommes. La bouilloire chante dans la cuisine. La vapeur fait un petit nuage. Papa essuie la table. Ça sent le thé. Une tasse fume encore. Maman plie le torchon. Le tiroir fait un petit clic. Près de la porte, la vitre est un peu floue. Tu vois le hall, Nina ? Oui. Je veux une pomme qui brille. On y va, avec le sac. En ce moment, Nina cherche le sac. Papa sort le sac bleu. Le tissu sent le coton. Prends de l'eau, le hall est long. Nina met la gourde. La gourde est froide. Elle voit une cuillère en bois. Elle la pose dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. Le hall n'en a pas besoin. Nina retire la cuillère. Où est le chapeau ? Le chapeau jaune n'est pas là. Sous la chaise, peut-être. Nina se penche. Le chapeau est souple, un peu poussiéreux. Elle le secoue, tout doux. Elle le met dans le sac. Ton doudou voudra la pomme aussi. Le doudou sent le coton. Il est tout doux. Nina le met dans le sac. Tu fermes ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Derrière la vitre floue, les caisses râpent le pavé. Même ici, ça sent la pomme du hall. Nina connaît cette cuisine, ses recoins. La bouilloire chante, petite. Un nuage de vapeur touche la vitre. Sur le verre, un &lt;emphasis level="moderate"&gt;éclat de caisse&lt;/emphasis&gt; cligne. Il vient du hall, si près. Nina ne sait pas à quoi il servira. Papa essuie la table. La nappe sent le thé chaud. Une tasse fume près du torchon. Maman plie le torchon, sans se presser. Le tiroir fait un petit clic. Nina, tu sens la pomme ? Oui, papa. Je veux une pomme, maintenant ! On y va, avec le sac. En ce moment, Nina saisit le sac bleu. Le tissu sent le coton, un peu rêche. Prends de l'eau, le hall est long. Nina prend la gourde froide. Le bouchon est lisse sous le doigt. Je mets tout, d'un coup ! Elle pousse la gourde, trop vite. Une cuillère en bois attend près du bol. Nina la jette dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. Le hall n'en a pas besoin. Nina veut fermer, sans attendre. Où est mon chapeau ? Le chapeau jaune n'est pas là. Nina bourre le sac, quand même. Le zip mord la sangle. Ça reste coincé ! Elle tire plus fort. Le zip refuse. Le sourire de Nina disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Papa se baisse à sa hauteur. Tu regardes le sac ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Clovis est dans l'entrée. Papa sort le &lt;emphasis&gt;sac&lt;/emphasis&gt; bleu. Papa, l'adulte, dit : on met la gourde. On met le chapeau. On met le doudou. Clovis écoute. Il met dans le sac ce que l'adulte a dit. La gourde est froide. Le chapeau est jaune. Le doudou sent le coton. Clovis ferme le sac. Parce qu'il a mis ce que papa a dit, le sac est prêt. Maman arrive. Elle dit : bravo. Ils sortent. Le sac est sur le dos de Clovis. [pause]</t>
+          <t>Derrière la vitre floue, les caisses râpent le pavé. Même ici, ça sent la pomme du hall. Nina connaît cette cuisine, ses recoins. La bouilloire chante, petite. Un nuage de vapeur touche la vitre. Sur le verre, un &lt;emphasis&gt;éclat de caisse&lt;/emphasis&gt; cligne. Il vient du hall, si près. Nina ne sait pas à quoi il servira. Papa essuie la table. La nappe sent le thé chaud. Une tasse fume près du torchon. Maman plie le torchon, sans se presser. Le tiroir fait un petit clic. Nina, tu sens la pomme ? Oui, papa. Je veux une pomme, maintenant ! On y va, avec le sac. En ce moment, Nina saisit le sac bleu. Le tissu sent le coton, un peu rêche. Prends de l'eau, le hall est long. Nina prend la gourde froide. Le bouchon est lisse sous le doigt. Je mets tout, d'un coup ! Elle pousse la gourde, trop vite. Une cuillère en bois attend près du bol. Nina la jette dans le sac. La cuillère fait un bruit dur. La cuillère reste à la cuisine. Le hall n'en a pas besoin. Nina veut fermer, sans attendre. Où est mon chapeau ? Le chapeau jaune n'est pas là. Nina bourre le sac, quand même. Le zip mord la sangle. Ça reste coincé ! Elle tire plus fort. Le zip refuse. Le sourire de Nina disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Papa se baisse à sa hauteur. Tu regardes le sac ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>éclat de caisse</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,52 +1321,59 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_la_pomme_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les caisses du hall râpent le pavé.
-narrateur|Même d'ici, ça sent les pommes.
-narrateur|La bouilloire chante dans la cuisine.
-narrateur|La vapeur fait un petit nuage.
+          <t>narrateur|Derrière la vitre floue, les caisses râpent le pavé.
+narrateur|Même ici, ça sent la pomme du hall.
+narrateur|Nina connaît cette cuisine, ses recoins.
+narrateur|La bouilloire chante, petite.
+narrateur|Un nuage de vapeur touche la vitre.
+narrateur|Sur le verre, un éclat de caisse cligne.
+narrateur|Il vient du hall, si près.
+narrateur|Nina ne sait pas à quoi il servira.
 narrateur|Papa essuie la table.
-narrateur|Ça sent le thé.
-narrateur|Une tasse fume encore.
-narrateur|Maman plie le torchon.
+narrateur|La nappe sent le thé chaud.
+narrateur|Une tasse fume près du torchon.
+narrateur|Maman plie le torchon, sans se presser.
 narrateur|Le tiroir fait un petit clic.
-narrateur|Près de la porte, la vitre est un peu floue.
-papa|Tu vois le hall, Nina ?
-enfant-f|Oui.
-enfant-f|Je veux une pomme qui brille.
+papa|Nina, tu sens la pomme ?
+enfant-f|Oui, papa.
+enfant-f|Je veux une pomme, maintenant !
 maman|On y va, avec le sac.
-narrateur|En ce moment, Nina cherche le sac.
-narrateur|Papa sort le sac bleu.
-narrateur|Le tissu sent le coton.
+narrateur|En ce moment, Nina saisit le sac bleu.
+narrateur|Le tissu sent le coton, un peu rêche.
 papa|Prends de l'eau, le hall est long.
-narrateur|Nina met la gourde.
-narrateur|La gourde est froide.
-narrateur|Elle voit une cuillère en bois.
-narrateur|Elle la pose dans le sac.
+narrateur|Nina prend la gourde froide.
+narrateur|Le bouchon est lisse sous le doigt.
+enfant-f|Je mets tout, d'un coup !
+narrateur|Elle pousse la gourde, trop vite.
+narrateur|Une cuillère en bois attend près du bol.
+narrateur|Nina la jette dans le sac.
 narrateur|La cuillère fait un bruit dur.
 papa|La cuillère reste à la cuisine.
 maman|Le hall n'en a pas besoin.
-narrateur|Nina retire la cuillère.
-enfant-f|Où est le chapeau ?
+narrateur|Nina veut fermer, sans attendre.
+enfant-f|Où est mon chapeau ?
 narrateur|Le chapeau jaune n'est pas là.
-maman|Sous la chaise, peut-être.
-narrateur|Nina se penche.
-narrateur|Le chapeau est souple, un peu poussiéreux.
-narrateur|Elle le secoue, tout doux.
-narrateur|Elle le met dans le sac.
-papa|Ton doudou voudra la pomme aussi.
-narrateur|Le doudou sent le coton.
-enfant-f|Il est tout doux.
-narrateur|Nina le met dans le sac.
-maman|Tu fermes ?</t>
+narrateur|Nina bourre le sac, quand même.
+narrateur|Le zip mord la sangle.
+enfant-f|Ça reste coincé !
+narrateur|Elle tire plus fort.
+narrateur|Le zip refuse.
+narrateur|Le sourire de Nina disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Papa se baisse à sa hauteur.
+papa|Tu regardes le sac ?</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>bouilloire,caisses,vitre</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1405,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nina prépare le sac. Où met-elle les affaires ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nina prépare le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Où met-elle les affaires ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Papa a parlé. Que met Clovis dans le &lt;emphasis&gt;sac&lt;/emphasis&gt; ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nina prépare le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Où met-elle les affaires ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1466,7 +1473,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1477,7 +1484,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1492,11 +1499,11 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1507,23 +1514,23 @@
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1538,17 +1545,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=les_affaires_vont_dans_le_sac; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1581,17 +1588,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina ferme le sac. Ça fait zzz. Le sac bleu est prêt. Le sac est prêt ? Oui, maman. Merci, Nina. Tu as laissé la cuillère ici. Le petit nuage de la bouilloire s'en va. On peut sortir, maintenant. La pomme m'attend. Oui, elle brille déjà, là-bas. Nina enfile le sac. Le sac est sur le dos de Nina. Tu as ton sac, Nina ? Oui, maman. On ouvre la porte. Papa ouvre la porte.</t>
+          <t>Nina refuse de tirer plus fort. Elle pose un genou au sol. La sangle est plate, sous le zip. Je la sors. Elle pousse le tissu, un peu. Le zip lâche, petit à petit. Il part. Sors la cuillère, d'abord. Nina retire la cuillère en bois. Elle la pose près de la tasse. Le chapeau, sous la chaise ? Nina se penche. Le chapeau est souple, un peu poussiéreux. Elle le secoue, au-dessus du sol. Le chapeau glisse dans le sac. Ton doudou voudra la pomme, lui aussi. Où est-il ? Le doudou n'est pas près des chaussures. Regarde sur la chaise, près du torchon. Nina cherche près du torchon. Le doudou sent le coton chaud. Il était caché. Elle le glisse dans le sac. La gourde reste au fond, froide. Le zip avance, sans mordre. Tu fermes, Nina ? Oui, maman. Nina appuie sur la fermeture. Ça fait un petit zzz. Le sac bleu est fermé. Merci, Nina. Le sac est prêt ? Oui, papa. Nina pose la main sur le tissu. Le tissu est un peu rêche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nina ferme le sac. Ça fait zzz. Le sac bleu est prêt. Le sac est prêt ? Oui, maman. Merci, Nina. Tu as laissé la cuillère ici. Le petit nuage de la bouilloire s'en va. On peut sortir, maintenant. La pomme m'attend. Oui, elle brille déjà, là-bas. Nina enfile le sac. Le sac est sur le dos de Nina. Tu as ton sac, Nina ? Oui, maman. On ouvre la porte. Papa ouvre la porte.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina refuse de tirer plus fort. Elle pose un genou au sol. La sangle est plate, sous le zip. Je la sors. Elle pousse le tissu, un peu. Le zip lâche, petit à petit. Il part. Sors la cuillère, d'abord. Nina retire la cuillère en bois. Elle la pose près de la tasse. Le chapeau, sous la chaise ? Nina se penche. Le chapeau est souple, un peu poussiéreux. Elle le secoue, au-dessus du sol. Le chapeau glisse dans le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Ton doudou voudra la pomme, lui aussi. Où est-il ? Le doudou n'est pas près des chaussures. Regarde sur la chaise, près du torchon. Nina cherche près du torchon. Le doudou sent le coton chaud. Il était caché. Elle le glisse dans le sac. La gourde reste au fond, froide. Le zip avance, sans mordre. Tu fermes, Nina ? Oui, maman. Nina appuie sur la fermeture. Ça fait un petit zzz. Le sac bleu est fermé. Merci, Nina. Le sac est prêt ? Oui, papa. Nina pose la main sur le tissu. Le tissu est un peu rêche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Clovis a préparé le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Il a mis ce que l'adulte a dit. Papa et maman étaient là. [pause]</t>
+          <t>Nina refuse de tirer plus fort. Elle pose un genou au sol. La sangle est plate, sous le zip. Je la sors. Elle pousse le tissu, un peu. Le zip lâche, petit à petit. Il part. Sors la cuillère, d'abord. Nina retire la cuillère en bois. Elle la pose près de la tasse. Le chapeau, sous la chaise ? Nina se penche. Le chapeau est souple, un peu poussiéreux. Elle le secoue, au-dessus du sol. Le chapeau glisse dans le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Ton doudou voudra la pomme, lui aussi. Où est-il ? Le doudou n'est pas près des chaussures. Regarde sur la chaise, près du torchon. Nina cherche près du torchon. Le doudou sent le coton chaud. Il était caché. Elle le glisse dans le sac. La gourde reste au fond, froide. Le zip avance, sans mordre. Tu fermes, Nina ? Oui, maman. Nina appuie sur la fermeture. Ça fait un petit zzz. Le sac bleu est fermé. Merci, Nina. Le sac est prêt ? Oui, papa. Nina pose la main sur le tissu. Le tissu est un peu rêche. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1638,7 +1645,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1646,10 +1653,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,23 +1686,23 @@
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1704,10 +1711,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1720,28 +1727,51 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=concentration puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_prépare_sans_foncer; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina ferme le sac.
-narrateur|Ça fait zzz.
-narrateur|Le sac bleu est prêt.
-maman|Le sac est prêt ?
+          <t>narrateur|Nina refuse de tirer plus fort.
+narrateur|Elle pose un genou au sol.
+narrateur|La sangle est plate, sous le zip.
+enfant-f|Je la sors.
+narrateur|Elle pousse le tissu, un peu.
+narrateur|Le zip lâche, petit à petit.
+enfant-f|Il part.
+papa|Sors la cuillère, d'abord.
+narrateur|Nina retire la cuillère en bois.
+narrateur|Elle la pose près de la tasse.
+maman|Le chapeau, sous la chaise ?
+narrateur|Nina se penche.
+narrateur|Le chapeau est souple, un peu poussiéreux.
+narrateur|Elle le secoue, au-dessus du sol.
+narrateur|Le chapeau glisse dans le sac.
+papa|Ton doudou voudra la pomme, lui aussi.
+enfant-f|Où est-il ?
+narrateur|Le doudou n'est pas près des chaussures.
+maman|Regarde sur la chaise, près du torchon.
+narrateur|Nina cherche près du torchon.
+narrateur|Le doudou sent le coton chaud.
+enfant-f|Il était caché.
+narrateur|Elle le glisse dans le sac.
+narrateur|La gourde reste au fond, froide.
+narrateur|Le zip avance, sans mordre.
+maman|Tu fermes, Nina ?
 enfant-f|Oui, maman.
+narrateur|Nina appuie sur la fermeture.
+narrateur|Ça fait un petit zzz.
+narrateur|Le sac bleu est fermé.
 papa|Merci, Nina.
-papa|Tu as laissé la cuillère ici.
-narrateur|Le petit nuage de la bouilloire s'en va.
-maman|On peut sortir, maintenant.
-enfant-f|La pomme m'attend.
-papa|Oui, elle brille déjà, là-bas.
-narrateur|Nina enfile le sac.
-narrateur|Le sac est sur le dos de Nina.
-maman|Tu as ton sac, Nina ?
-enfant-f|Oui, maman.
-papa|On ouvre la porte.
-narrateur|Papa ouvre la porte.</t>
+papa|Le sac est prêt ?
+enfant-f|Oui, papa.
+narrateur|Nina pose la main sur le tissu.
+narrateur|Le tissu est un peu rêche.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>zip,sac</t>
         </is>
       </c>
     </row>
@@ -1768,17 +1798,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ils sortent. L'air sent les caisses et le fruit. Le hall n'est plus flou. Il est vrai, maintenant. Oui, on y va ensemble. Une pomme rouge brille sur une caisse. Nina s'accroupit. Elle touche la peau lisse. Elle est un peu froide, un peu sucrée. Elle brille, maman. Tu la choisis ? Celle-là. Nina ferme la main autour de la pomme. Le fruit reste un moment, tout rond. On la sent ensemble ? Oui. Nina approche la pomme de son nez. Ça sent le sucre et la peau. Tu l'as trouvée. Une caisse râpe encore le pavé, tout loin.</t>
+          <t>On met tes chaussures ? Nina enfile ses chaussures. Une semelle est froide. Tu as fini tes chaussures ? Oui, maman. On ouvre la porte. Papa ouvre la porte. L'air sent les caisses et le fruit. Le hall n'est plus flou. Il est vrai ! Oui, on y va ensemble. Nina enfile le sac. Le sac tape contre son dos. Ils marchent vers le hall aux caisses. Le pavé est un peu poudreux. Je la prends ! Une pomme rouge brille, trop près. Nina tend la main, trop vite. La pomme glisse, roule sous une caisse. Oh. Elle veut foncer, à quatre pattes. Nina refuse de foncer. Attends, je regarde. Sur le bois, un éclat de caisse cligne. C'est celui de la vitre. Comme à la cuisine ! Tu le vois, toi ? Oui, sur cette caisse. Nina s'accroupit, lente. Elle écoute le hall, un instant. Une autre caisse râpe, plus loin. La pomme attend sous le bois. Nina glisse la main, lente. Ses doigts trouvent la peau lisse.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Ils sortent. L'air sent les caisses et le fruit. Le hall n'est plus flou. Il est vrai, maintenant. Oui, on y va ensemble. Une pomme rouge brille sur une caisse. Nina s'accroupit. Elle touche la peau lisse. Elle est un peu froide, un peu sucrée. Elle brille, maman. Tu la choisis ? Celle-là. Nina ferme la main autour de la pomme. Le fruit reste un moment, tout rond. On la sent ensemble ? Oui. Nina approche la pomme de son nez. Ça sent le sucre et la peau. Tu l'as trouvée. Une caisse râpe encore le pavé, tout loin.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;On met tes chaussures ? Nina enfile ses chaussures. Une semelle est froide. Tu as fini tes chaussures ? Oui, maman. On ouvre la porte. Papa ouvre la porte. L'air sent les caisses et le fruit. Le hall n'est plus flou. Il est vrai ! Oui, on y va ensemble. Nina enfile le sac. Le sac tape contre son dos. Ils marchent vers le hall aux caisses. Le pavé est un peu poudreux. Je la prends ! Une pomme rouge brille, trop près. Nina tend la main, trop vite. La pomme glisse, roule sous une caisse. Oh. Elle veut foncer, à quatre pattes. Nina refuse de foncer. Attends, je regarde. Sur le bois, un &lt;emphasis level="moderate"&gt;éclat de caisse&lt;/emphasis&gt; cligne. C'est celui de la vitre. Comme à la cuisine ! Tu le vois, toi ? Oui, sur cette caisse. Nina s'accroupit, lente. Elle écoute le hall, un instant. Une autre caisse râpe, plus loin. La pomme attend sous le bois. Nina glisse la main, lente. Ses doigts trouvent la peau lisse.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Clovis enfile le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Papa ouvre la porte. [pause]</t>
+          <t>&lt;low-pitch&gt;On met tes chaussures ? Nina enfile ses chaussures. Une semelle est froide. Tu as fini tes chaussures ? Oui, maman. On ouvre la porte. Papa ouvre la porte. L'air sent les caisses et le fruit. Le hall n'est plus flou. Il est vrai ! Oui, on y va ensemble. Nina enfile le sac. Le sac tape contre son dos. Ils marchent vers le hall aux caisses. Le pavé est un peu poudreux. Je la prends ! Une pomme rouge brille, trop près. Nina tend la main, trop vite. La pomme glisse, roule sous une caisse. Oh. Elle veut foncer, à quatre pattes. Nina refuse de foncer. Attends, je regarde. Sur le bois, un &lt;emphasis&gt;éclat de caisse&lt;/emphasis&gt; cligne. C'est celui de la vitre. Comme à la cuisine ! Tu le vois, toi ? Oui, sur cette caisse. Nina s'accroupit, lente. Elle écoute le hall, un instant. Une autre caisse râpe, plus loin. La pomme attend sous le bois. Nina glisse la main, lente. Ses doigts trouvent la peau lisse.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1825,7 +1855,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1833,22 +1863,26 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1859,30 +1893,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>éclat de caisse</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1891,43 +1925,66 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_retrouve_l_eclat; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ils sortent.
+          <t>papa|On met tes chaussures ?
+narrateur|Nina enfile ses chaussures.
+narrateur|Une semelle est froide.
+maman|Tu as fini tes chaussures ?
+enfant-f|Oui, maman.
+papa|On ouvre la porte.
+narrateur|Papa ouvre la porte.
 narrateur|L'air sent les caisses et le fruit.
 narrateur|Le hall n'est plus flou.
-enfant-f|Il est vrai, maintenant.
+enfant-f|Il est vrai !
 papa|Oui, on y va ensemble.
-narrateur|Une pomme rouge brille sur une caisse.
-narrateur|Nina s'accroupit.
-narrateur|Elle touche la peau lisse.
-narrateur|Elle est un peu froide, un peu sucrée.
-enfant-f|Elle brille, maman.
-maman|Tu la choisis ?
-enfant-f|Celle-là.
-narrateur|Nina ferme la main autour de la pomme.
-narrateur|Le fruit reste un moment, tout rond.
-papa|On la sent ensemble ?
-enfant-f|Oui.
-narrateur|Nina approche la pomme de son nez.
-narrateur|Ça sent le sucre et la peau.
-maman|Tu l'as trouvée.
-narrateur|Une caisse râpe encore le pavé, tout loin.</t>
+narrateur|Nina enfile le sac.
+narrateur|Le sac tape contre son dos.
+narrateur|Ils marchent vers le hall aux caisses.
+narrateur|Le pavé est un peu poudreux.
+enfant-f|Je la prends !
+narrateur|Une pomme rouge brille, trop près.
+narrateur|Nina tend la main, trop vite.
+narrateur|La pomme glisse, roule sous une caisse.
+enfant-f|Oh.
+narrateur|Elle veut foncer, à quatre pattes.
+narrateur|Nina refuse de foncer.
+enfant-f|Attends, je regarde.
+narrateur|Sur le bois, un éclat de caisse cligne.
+narrateur|C'est celui de la vitre.
+enfant-f|Comme à la cuisine !
+maman|Tu le vois, toi ?
+enfant-f|Oui, sur cette caisse.
+narrateur|Nina s'accroupit, lente.
+narrateur|Elle écoute le hall, un instant.
+narrateur|Une autre caisse râpe, plus loin.
+narrateur|La pomme attend sous le bois.
+narrateur|Nina glisse la main, lente.
+narrateur|Ses doigts trouvent la peau lisse.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>hall,caisses,pas</t>
         </is>
       </c>
     </row>
@@ -1954,17 +2011,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nina ouvre encore la main. La pomme rouge brille dans sa paume. Elle est à moi. Oui, tu es arrivée au hall. Le sac bleu tape le dos de Nina. Le thé de la cuisine est loin, maintenant. Merci pour le sac, Nina. La peau lisse reste froide contre sa main.</t>
+          <t>Nina ferme la main autour de la pomme. Le fruit reste rond, un peu froid. Elle brille, maman. Tu la choisis ? Celle-là. On la sent ensemble ? Oui. Nina approche la pomme de son nez. Ça sent le sucre et la peau. Sur le bois, l'éclat de caisse reste. Comme sur la vitre, papa. Tu le portes, toi ? Oui, dans mon sac. Nina ouvre le sac, un peu. Elle glisse la pomme contre le doudou. Le sac repose contre sa hanche. On la sent, papa. Tu la sens sur tes joues ? Oui, elle est froide. L'éclat de caisse laisse une trace claire, sur la peau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Nina ouvre encore la main. La pomme rouge brille dans sa paume. Elle est à moi. Oui, tu es arrivée au hall. Le sac bleu tape le dos de Nina. Le thé de la cuisine est loin, maintenant. Merci pour le sac, Nina. La peau lisse reste froide contre sa main.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina ferme la main autour de la pomme. Le fruit reste rond, un peu froid. Elle brille, maman. Tu la choisis ? Celle-là. On la sent ensemble ? Oui. Nina approche la pomme de son nez. Ça sent le sucre et la peau. Sur le bois, l'&lt;emphasis level="moderate"&gt;éclat de caisse&lt;/emphasis&gt; reste. Comme sur la vitre, papa. Tu le portes, toi ? Oui, dans mon sac. Nina ouvre le sac, un peu. Elle glisse la pomme contre le doudou. Le sac repose contre sa hanche. On la sent, papa. Tu la sens sur tes joues ? Oui, elle est froide. L'éclat de caisse laisse une trace claire, sur la peau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina ferme la main autour de la pomme. Le fruit reste rond, un peu froid. Elle brille, maman. Tu la choisis ? Celle-là. On la sent ensemble ? Oui. Nina approche la pomme de son nez. Ça sent le sucre et la peau. Sur le bois, l'&lt;emphasis&gt;éclat de caisse&lt;/emphasis&gt; reste. Comme sur la vitre, papa. Tu le portes, toi ? Oui, dans mon sac. Nina ouvre le sac, un peu. Elle glisse la pomme contre le doudou. Le sac repose contre sa hanche. On la sent, papa. Tu la sens sur tes joues ? Oui, elle est froide. L'éclat de caisse laisse une trace claire, sur la peau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2011,18 +2068,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2031,12 +2088,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2045,17 +2102,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de caisse</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2064,11 +2125,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2077,31 +2138,52 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_de_la_vitre_est_sur_la_caisse; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Nina ouvre encore la main.
-narrateur|La pomme rouge brille dans sa paume.
-enfant-f|Elle est à moi.
-papa|Oui, tu es arrivée au hall.
-narrateur|Le sac bleu tape le dos de Nina.
-narrateur|Le thé de la cuisine est loin, maintenant.
-maman|Merci pour le sac, Nina.
-narrateur|La peau lisse reste froide contre sa main.</t>
+          <t>narrateur|Nina ferme la main autour de la pomme.
+narrateur|Le fruit reste rond, un peu froid.
+enfant-f|Elle brille, maman.
+maman|Tu la choisis ?
+enfant-f|Celle-là.
+papa|On la sent ensemble ?
+enfant-f|Oui.
+narrateur|Nina approche la pomme de son nez.
+narrateur|Ça sent le sucre et la peau.
+narrateur|Sur le bois, l'éclat de caisse reste.
+enfant-f|Comme sur la vitre, papa.
+papa|Tu le portes, toi ?
+enfant-f|Oui, dans mon sac.
+narrateur|Nina ouvre le sac, un peu.
+narrateur|Elle glisse la pomme contre le doudou.
+narrateur|Le sac repose contre sa hanche.
+enfant-f|On la sent, papa.
+maman|Tu la sens sur tes joues ?
+enfant-f|Oui, elle est froide.
+narrateur|L'éclat de caisse laisse une trace claire, sur la peau.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>pomme,caisse</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2214,6 +2296,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
